--- a/output/pdf_financials_xlsx/AIME.P.xlsx
+++ b/output/pdf_financials_xlsx/AIME.P.xlsx
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.146426</v>
+        <v>-0.146426</v>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.146426</v>
+        <v>-0.146426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AIME.P.xlsx
+++ b/output/pdf_financials_xlsx/AIME.P.xlsx
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005572</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008168</v>
       </c>
     </row>
     <row r="13">
@@ -1120,10 +1120,10 @@
         <v>-0.052804</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.0275</v>
+        <v>-0.033072</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.036932</v>
+        <v>-0.0451</v>
       </c>
     </row>
     <row r="28">
@@ -1170,10 +1170,10 @@
         <v>-0.052804</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.0275</v>
+        <v>-0.033072</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.036932</v>
+        <v>-0.0451</v>
       </c>
     </row>
     <row r="30">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
